--- a/data_extactor/batch_10_fa/trimmed/batch_0068_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0068_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | شنیدن فعال | تفکر انتقادی | سخن گفتن | نگارش | یادگیری فعال | ریاضیات</t>
+          <t>درک مطلب | نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن | نگارش | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | امور اداری و دفتری | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | زبان انگلیسی | جغرافیا | حقوق و مقررات دولتی</t>
+          <t>حمل و نقل | اداری | خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | جغرافیا | قانون و دولت</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | مرتب‌سازی اطلاعات | حساسیت به مسئله | استدلال قیاسی | بیان کتبی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | استدلال قیاسی | بیان کتبی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>متصدیان باربری و حمل‌ونقل کالا | کارگزاران گمرکی (حق‌العمل‌کاران گمرک) | متصدیان دیسپاچ و اعزام (به‌جز پلیس، آتش‌نشانی و اورژانس) | کارشناسان لجستیک | تحلیل‌گران لجستیک | کارمندان امور تدارکات و خرید | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>کارگزاران حمل‌ونقل و بار | حق‌العمل‌کاران و کارگزاران گمرکی | متصدیان دیسپاچ و اعزام | کارشناسان لجستیک و مدیریت زنجیره تأمین | تحلیل‌گران لجستیک و فرایند توزیع | کارمندان تدارکات و کارپردازی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,22 +560,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>نرم‌افزار Microsoft Excel | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Outlook | نرم‌افزار Microsoft Word | نرم‌افزارهای مسیریابی و نقشه‌خوانی</t>
+          <t>نرم‌افزار Microsoft Excel | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Outlook | نرم‌افزار Microsoft Word | نرم‌افزار نقشه‌برداری مسیر</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | تفکر انتقادی | نگارش | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | حمل‌ونقل | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | حمل و نقل | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | دید دور | چابکی دستی | مرتب‌سازی اطلاعات | حساسیت به مسئله</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | بینایی دور | مهارت دستی | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>متصدیان باربری و حمل‌ونقل کالا | رانندگان توزیع و ویزیتورها | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | رانندگان کامیونت و وانت‌بار | متصدیان باجه پست | نامه‌رسان‌های پست | کارمندان ارسال، دریافت و انبارداری</t>
+          <t>کارگزاران حمل‌ونقل و بار | رانندگان توزیع و فروش مویرگی | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | رانندگان خودروهای باربری سبک و وانت‌بارها | متصدیان باجه و امور پستی | نامه‌رسان‌ها و موزعین پست | کارمندان انبار، ارسال و دریافت کالا</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حقوق و مقررات دولتی | مخابرات و ارتباطات دوربرد | خدمات مشتریان و خدمات فردی | جغرافیا | رایانه و الکترونیک | روان‌شناسی</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | مخابرات | خدمات مشتری و شخصی | جغرافیا | رایانه و الکترونیک | روان‌شناسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | حساسیت به مسئله | توجه انتخابی | استدلال قیاسی | تقسیم زمان و توجه</t>
+          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | حساسیت به مسئله | توجه انتخابی | استدلال قیاسی | تقسیم توجه</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>رانندگان و خدمه آمبولانس (به‌جز تکنسین‌های فوریت‌های پزشکی) | متصدیان دیسپاچ و اعزام (به‌جز پلیس، آتش‌نشانی و اورژانس) | مدیران مدیریت بحران و پدافند غیرعامل | تکنسین‌های فوریت‌های پزشکی | افسران گشت پلیس | مأموران حراست و نگهبانان | متصدیان تلفنخانه و مراکز پاسخگویی</t>
+          <t>رانندگان و خدمه آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | متصدیان دیسپاچ و اعزام | مدیران مدیریت بحران و پدافند غیرعامل | تکنسین‌های فوریت‌های پزشکی | ماموران گشت پلیس و کلانتری | نگهبانان و ماموران حراست | اپراتورهای مراکز تلفن و پاسخگویی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | نظارت | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | مدیریت و امور اداری | امور اداری و دفتری | حمل‌ونقل | رایانه و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | ایمنی و امنیت عمومی | مدیریت و اداره | اداری | حمل و نقل | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>سرپرستان باربری و تخلیه و بارگیری هوایی | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی مواد | رانندگان کامیون سنگین و تریلی | متصدیان توزیع و دیسپاچینگ شبکه برق | کارمندان برنامه‌ریزی، تولید و پیگیری امور | اپراتورهای فوریت‌های پلیسی و امدادی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>سرپرستان بارگیری و جابه‌جایی بار هواپیما | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | رانندگان خودروهای سنگین و کشنده‌ها | دیسپچرها و توزیع‌کنندگان شبکه برق | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | اپراتورهای فوریت‌های پلیسی و امدادی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | زبان انگلیسی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی | ریاضیات</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | بیان شفاهی | سرعت ادراک | مرتب‌سازی اطلاعات | دید دور | درک کتبی</t>
+          <t>بینایی نزدیک | درک شفاهی | بیان شفاهی | سرعت ادراکی | ترتیب‌دهی اطلاعات | بینایی دور | درک کتبی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>نصابان و تعمیرکاران خطوط انتقال و توزیع برق | کاردان‌ها و تکنسین‌های مهندسی برق و الکترونیک | بازرسان، آزمون‌گران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | کارگران تعمیرات و نگهداری عمومی | متصدیان توزیع و دیسپاچینگ شبکه برق | اپراتورهای پمپ‌ها و ایستگاه‌های پمپاژ (به‌جز پمپ‌های سرچاهی) | اپراتورهای تصفیه‌خانه‌ها و شبکه‌های آب و فاضلاب</t>
+          <t>تکنسین‌ها و سیم‌بانان خطوط انتقال و توزیع برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | کارگران عمومی تعمیرات و نگهداری تاسیسات | دیسپچرها و توزیع‌کنندگان شبکه برق | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ریاضیات | فروش و بازاریابی | امور اداری و دفتری | رایانه و الکترونیک | حمل‌ونقل</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | فروش و بازاریابی | اداری | رایانه و الکترونیک | حمل و نقل</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | وضوح گفتار | تشخیص گفتار | درک کتبی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | درک کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>صندوق‌داران | نامه‌رسان‌ها و پیک‌ها | کارمندان بایگانی | کارمندان پستی و اپراتورهای ماشین‌های تمبر و بسته‌بندی اداری | نامه‌رسان‌های پست | تفکیک‌کنندگان، پردازش‌گران و اپراتورهای دستگاه‌های مرتب‌سازی پست | روسای دفاتر و ادارات پست</t>
+          <t>صندوق‌داران | پیک‌ها و نامه‌رسان‌ها | متصدیان بایگانی و اسناد | کارمندان امور مراسلات و متصدیان ماشین‌های پستی، به جز پست دولتی | نامه‌رسان‌ها و موزعین پست | اپراتورها و متصدیان تفکیک و پردازش پستی | مدیران و رؤسای دفاتر پستی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ایمنی و امنیت عمومی | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>مرتب‌سازی اطلاعات | دید نزدیک | قدرت عضلانی تنه | انعطاف‌پذیری در طبقه‌بندی | حساسیت به مسئله | درک کتبی | درک شفاهی</t>
+          <t>ترتیب‌دهی اطلاعات | بینایی نزدیک | قدرت تنه | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | درک کتبی | درک شفاهی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>نامه‌رسان‌ها و پیک‌ها | کارشناسان خدمات مشتریان | رانندگان توزیع و ویزیتورها | رانندگان کامیونت و وانت‌بار | متصدیان باجه پست | تفکیک‌کنندگان، پردازش‌گران و اپراتورهای دستگاه‌های مرتب‌سازی پست | روسای دفاتر و ادارات پست</t>
+          <t>پیک‌ها و نامه‌رسان‌ها | کارشناسان خدمات و پشتیبانی مشتریان | رانندگان توزیع و فروش مویرگی | رانندگان خودروهای باربری سبک و وانت‌بارها | متصدیان باجه و امور پستی | اپراتورها و متصدیان تفکیک و پردازش پستی | مدیران و رؤسای دفاتر پستی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | چابکی دستی | توانایی و استقامت بدنی | هماهنگی چند عضو بدن | سرعت ادراک | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات</t>
+          <t>بینایی نزدیک | مهارت دستی | قدرت ایستا | هماهنگی چند عضو | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>اپراتورها و مراقبان نوار نقاله | کارگران جابه‌جایی دستی بار و اثاثیه | کارمندان پستی و اپراتورهای ماشین‌های تمبر و بسته‌بندی اداری | کارگران بسته‌بندی دستی | متصدیان باجه پست | نامه‌رسان‌های پست | کارمندان ارسال، دریافت و انبارداری</t>
+          <t>اپراتورها و متصدیان نوار نقاله | کارگران جابه‌جایی دستی بار، کالا و مصالح | کارمندان امور مراسلات و متصدیان ماشین‌های پستی، به جز پست دولتی | کارگران بسته‌بندی دستی | متصدیان باجه و امور پستی | نامه‌رسان‌ها و موزعین پست | کارمندان انبار، ارسال و دریافت کالا</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | شنیدن فعال | تفکر انتقادی | نگارش | نظارت</t>
+          <t>درک مطلب | سخن گفتن | گوش دادن فعال | تفکر انتقادی | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>تولید و فراوری | خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور اداری و دفتری | مدیریت و امور اداری | رایانه و الکترونیک</t>
+          <t>تولید و فرآوری | خدمات مشتری و شخصی | زبان انگلیسی | اداری | مدیریت و اداره | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | مرتب‌سازی اطلاعات | بیان شفاهی | حساسیت به مسئله | درک کتبی | بیان کتبی | استدلال قیاسی</t>
+          <t>درک شفاهی | ترتیب‌دهی اطلاعات | بیان شفاهی | حساسیت به مسئله | درک کتبی | بیان کتبی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>متصدیان دیسپاچ و اعزام (به‌جز پلیس، آتش‌نشانی و اورژانس) | سرپرستان رده‌اول کارکنان تولید و عملیات | مدیران تولید صنعتی | کارشناسان لجستیک | کارمندان امور تدارکات و خرید | کارمندان ارسال، دریافت و انبارداری | مدیران زنجیره تأمین</t>
+          <t>متصدیان دیسپاچ و اعزام | سرپرستان رده اول کارگران تولید و عملیات | مدیران تولید صنعتی | کارشناسان لجستیک و مدیریت زنجیره تأمین | کارمندان تدارکات و کارپردازی | کارمندان انبار، ارسال و دریافت کالا | مدیران زنجیره تامین</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | شنیدن فعال | نظارت | تفکر انتقادی</t>
+          <t>سخن گفتن | درک مطلب | گوش دادن فعال | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>امور اداری و دفتری | رایانه و الکترونیک | تولید و فراوری | ریاضیات | زبان انگلیسی</t>
+          <t>اداری | رایانه و الکترونیک | تولید و فرآوری | ریاضیات | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دید نزدیک | بیان شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات | درک شفاهی | چابکی دستی | توجه انتخابی</t>
+          <t>بینایی نزدیک | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | درک شفاهی | مهارت دستی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>متصدیان باربری و حمل‌ونقل کالا | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | کارگران جابه‌جایی دستی بار و اثاثیه | کارمندان ثبت سفارشات | کارمندان امور تدارکات و خرید | کارمندان برنامه‌ریزی، تولید و پیگیری امور | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>کارگزاران حمل‌ونقل و بار | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | کارگران جابه‌جایی دستی بار، کالا و مصالح | متصدیان ثبت و پیگیری سفارش‌ها | کارمندان تدارکات و کارپردازی | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
